--- a/Result/profitability/1325.xlsx
+++ b/Result/profitability/1325.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,7 +672,7 @@
         <v>-0.1450000000000002</v>
       </c>
       <c r="N2" t="n">
-        <v>-14.11125</v>
+        <v>-15.065</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>0.35</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.07375000000000022</v>
+        <v>-0.04250000000000023</v>
       </c>
       <c r="N3" t="n">
-        <v>-9.449999999999999</v>
+        <v>-10.81125</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>0.45</v>
       </c>
       <c r="M4" t="n">
-        <v>0.04124999999999979</v>
+        <v>0.01624999999999979</v>
       </c>
       <c r="N4" t="n">
-        <v>-4.8275</v>
+        <v>-7.286249999999999</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>0.46</v>
       </c>
       <c r="M5" t="n">
-        <v>0.1012499999999998</v>
+        <v>0.1462499999999998</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.5775000000000001</v>
+        <v>-2.3575</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
@@ -1137,10 +1137,10 @@
         <v>0.42</v>
       </c>
       <c r="M6" t="n">
-        <v>0.2262499999999998</v>
+        <v>0.2037499999999998</v>
       </c>
       <c r="N6" t="n">
-        <v>4.30625</v>
+        <v>4.56125</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,13 +1264,13 @@
         <v>0.22</v>
       </c>
       <c r="M7" t="n">
-        <v>0.2587499999999998</v>
+        <v>0.2374999999999998</v>
       </c>
       <c r="N7" t="n">
-        <v>10.7875</v>
+        <v>10.9</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P7" t="n">
         <v>1</v>
@@ -1282,7 +1282,7 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.32</v>
       </c>
       <c r="M8" t="n">
-        <v>0.3049999999999998</v>
+        <v>0.2874999999999998</v>
       </c>
       <c r="N8" t="n">
-        <v>17.16625</v>
+        <v>16.30875</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>1325</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>66</v>
+      </c>
+      <c r="D75" t="n">
+        <v>84</v>
+      </c>
+      <c r="E75" t="n">
+        <v>-18</v>
+      </c>
+      <c r="F75" t="n">
+        <v>-26.87</v>
+      </c>
+      <c r="G75" t="n">
+        <v>-31</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-46.82%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>7</v>
+      </c>
+      <c r="J75" t="n">
+        <v>-24</v>
+      </c>
+      <c r="K75" t="n">
+        <v>-19</v>
+      </c>
+      <c r="L75" t="n">
+        <v>-0.22</v>
+      </c>
+      <c r="M75" t="n">
+        <v>-0.2100000000000002</v>
+      </c>
+      <c r="N75" t="n">
+        <v>-19.82625</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-0.14</v>
+      </c>
+      <c r="X75" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-6.859999999999999</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.3428285857071465</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-0.6206896551724137</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-14.24</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>1.127474267616785</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
